--- a/AI Audit Log_PhamLeQuocThong.xlsx
+++ b/AI Audit Log_PhamLeQuocThong.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KÌ 7\SWD392\nopbaitap\ai-audit-log-tuilavetne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4542B6E9-4BF0-45FF-9D47-B4FCCE8D85A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7B76F7-E1D0-4C2C-B860-0FD43F6683A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 2" sheetId="1" r:id="rId1"/>
     <sheet name="Week 3" sheetId="2" r:id="rId2"/>
     <sheet name="Week 4" sheetId="3" r:id="rId3"/>
     <sheet name="Week 5" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 6" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 7" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -777,19 +779,166 @@
     <t>Phản hồi: AI cung cấp code PlantUML với cấu trúc khai báo
 actor, boundary, control, entity và các mũi tên -&gt;, --&gt;.
 Quyết định: Tôi tái sử dụng và tinh chỉnh mã này để chèn thẳng vào tài liệu phân tích thiết kế, tiết kiệm thời gian vẽ tay.</t>
+  </si>
+  <si>
+    <t>Slot 11</t>
+  </si>
+  <si>
+    <t>"Hãy giải thích State Diagram trong UML. 
+Nó được dùng để mô hình hóa điều gì trong hệ thống phần mềm?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích state diagram là 1 loại behavioral diagram trong UML, dùng để mô tả các trạng thái của một object và sự chuyển đổi giữa các trạng thái đó theo thời gian, dựa trên event. Nó đặc biệt phù hợp với các object có vòng đời rõ ràng như Order, User Session hoặc Payment.
+Quyết định: Tôi sử dụng state diagram để mô hình hóa các object có hành vi thay đổi theo trạng thái trong hệ thống, giúp hiểu rõ lifecycle thay vì chỉ nhìn vào class structure.</t>
+  </si>
+  <si>
+    <t>"Trong state diagram, state là gì? Hãy hướng dẫn cách xác định state cho 1 object"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho rằng state là 1 condition mà object tồn tại trong 1 khoảng thời gian và có thể phản ứng với event. State thường được xác định từ business status hoặc các giai đoạn xử lý.
+Quyết định: Tôi xác định state dựa trên nghiệp vụ thực tế như Pending, Processing, Completed thay vì chỉ dựa vào attribute đơn lẻ.</t>
+  </si>
+  <si>
+    <t>"Event trong state diagram là gì? Nó ảnh
+hưởng đến transition như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích event là 1 sự kiện xảy ra tại 1 thời điểm
+và có thể kích hoạt transition giữa các state. Transition thể hiện sự thay đổi trạng thái do event gây ra.
+Quyết định: Tôi luôn ghi rõ event trên các transition như submitOrder, cancelOrder, confirmPayment để đảm bảo sơ đồ rõ ràng và đúng logic hệ thống.</t>
+  </si>
+  <si>
+    <t>"Guard condition trong state diagram là gì? Khi nào nên sử dụng?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích guard condition là điều kiện boolean đi
+kèm event, chỉ khi điều kiện đúng thì transition mới xảy ra. Ví dụ: confirmPayment [amount &gt;= total].
+Quyết định: Tôi sử dụng guard condition để tránh sai logic nghiệp vụ, đặc biệt trong các trường hợp kiểm tra dữ liệu trước khi chuyển state.</t>
+  </si>
+  <si>
+    <t>"Phân biệt entry action và exit action trong
+state diagram"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết entry action được thực hiện khi vào state, 
+exit action khi rời state. Điều này giúp tránh lặp lại action ở nhiều transition.
+Quyết định: Tôi áp dụng entry action cho các xử lý chung như entry/Completed: sendNotification() để tối ưu sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Hãy giải thích Activity Diagram trong UML 
+và mục đích sử dụng"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả activity diagram dùng để biểu diễn workflow
+hoặc luồng xử lý của hệ thống, từ bước bắt đầu đến kết thúc, bao gồm các nhánh điều kiện và song song.
+Quyết định: Tôi dùng activity diagram để mô tả business process thay vì hành vi từng object như state diagram.</t>
+  </si>
+  <si>
+    <t>"Decision node và merge node trong activity diagram có vai trò gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích decision node dùng để rẽ nhánh theo
+điều kiện, còn merge node dùng để hợp các nhánh lại.
+Quyết định: Tôi sử dụng decision node cho các trường hợp if/else và merge node để đảm bảo luồng không bị rối hoặc sai logic.</t>
+  </si>
+  <si>
+    <t>"Fork và join trong activity diagram dùng
+để làm gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết fork dùng để tách luồng thành các hoạt
+động song song, join dùng để đồng bộ lại các luồng đó.
+Quyết định: Tôi áp dụng fork/join khi hệ thống thực hiện nhiều tác vụ cùng lúc như gửi email và lưu dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Swimlane trong activity diagram có ý 
+nghĩa gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích swimlane dùng để phân chia trách nhiệm
+giữa các actor hoặc hệ thống con.
+Quyết định: Tôi sử dụng swimlane để thể hiện rõ ai thực hiện bước nào (User, System, Admin), giúp dễ hiểu hơn khi trình bày.</t>
+  </si>
+  <si>
+    <t>"So sánh State Diagram và Activity Diagram, khi nào nên dùng mỗi loại?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ ra state diagram tập trung vào trạng thái của 
+object, còn activity diagram tập trung vào luồng xử lý. State diagram phù hợp với lifecycle, activity diagram phù hợp với workflow.
+Quyết định: Tôi kết hợp cả hai loại biểu đồ: dùng state diagram cho object quan trọng (Order, Payment) và activity diagram cho các quy trình nghiệp vụ (Place Order, Payment Process).</t>
+  </si>
+  <si>
+    <t>Slot 13</t>
+  </si>
+  <si>
+    <t>"Hãy giải thích Component Diagram trong UML. Nó được dùng để mô hình hóa điều gì trong hệ thống phần mềm?"</t>
+  </si>
+  <si>
+    <t>AI giải thích component diagram là 1 loại structural diagram 
+trong UML, dùng để mô tả các thành phần và mối quan hệ phụ thuộc giữa chúng ở mức kiến trúc hệ thống.
+Quyết định: Tôi sử dụng component diagram để mô hình hóa kiến trúc tổng thể thay vì đi vào chi tiết class.</t>
+  </si>
+  <si>
+    <t>"Component trong UML là gì? Hãy hướng dẫn
+cách xác định component cho hệ thống"</t>
+  </si>
+  <si>
+    <t>AI cho rằng component là 1 phần độc lập có thể triển khai riêng 
+như module hoặc service, thường xác định theo chức năng hệ thống.
+Quyết định: Tôi xác định component dựa trên các module nghiệp vụ như User, Order, Payment.</t>
+  </si>
+  <si>
+    <t>"Interface trong component diagram là gì? Nó được dùng như thế nào?"</t>
+  </si>
+  <si>
+    <t>"Dependency giữa các component là gì? Khi
+nào nên sử dụng?"</t>
+  </si>
+  <si>
+    <t>"Phân biệt component và class trong UML"</t>
+  </si>
+  <si>
+    <t>AI giải thích class là đơn vị logic nhỏ, còn component là đơn vị 
+lớn hơn có thể chứa nhiều class.
+Quyết định: Tôi dùng class diagram cho chi tiết và component diagram cho tổng thể.</t>
+  </si>
+  <si>
+    <t>AI cho biết dependency thể hiện sự phụ thuộc giữa các component bằng mũi tên nét đứt.
+Quyết định: Tôi sử dụng dependency để mô tả luồng gọi API giữa các module.</t>
+  </si>
+  <si>
+    <t>AI giải thích interface là điểm giao tiếp giữa các component, 
+gồm provided và required interface.
+Quyết định: Tôi sử dụng interface để thể hiện rõ cách các component tương tác.</t>
+  </si>
+  <si>
+    <t>"Port trong component diagram là gì và có vai
+trò gì?"</t>
+  </si>
+  <si>
+    <t>AI cho biết port là điểm kết nối giúp component giao tiếp với bên
+ngoài 1 cách rõ ràng.
+Quyết định: Tôi dùng port khi cần mô tả nhiều điểm giao tiếp khác nhau của một component.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -868,7 +1017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -877,20 +1026,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1457,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" customWidth="1"/>
@@ -1591,18 +1740,6 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1610,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
@@ -1702,11 +1839,287 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFAE320A-C878-4365-9536-22BE82E94BCF}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="50.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F13BAD4B-A4A5-43F3-A5E8-5554F4B7EB87}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.109375" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" customWidth="1"/>
+    <col min="4" max="4" width="50.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
